--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/09_Segundo_Turno_Lula_vs_Flavio_por_Sexo.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/09_Segundo_Turno_Lula_vs_Flavio_por_Sexo.xlsx
@@ -17,7 +17,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linhas_publicadas" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados_Mulheres'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo_Mulheres'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto_Mulheres'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Suavizados_Homens'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IC_Baixo_Homens'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IC_Alto_Homens'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cobertura'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Metodologia'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Linhas_publicadas'!$A$1:$X$19</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,7 +38,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +49,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -62,17 +81,35 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,94 +475,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>55.01138952164008</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>44.98861047835991</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>56.34698871460945</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>43.65301128539055</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>56.77825188217926</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>43.22174811782074</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>59.48436200364252</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>40.51563799635748</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>60.30185137238478</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>39.69814862761523</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>60.12987678797171</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>39.87012321202831</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>60.11852019768426</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>39.88147980231572</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>59.95005457814511</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>40.0499454218549</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>59.6198259746888</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>40.3801740253112</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -536,94 +611,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>52.07284666613531</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>42.05006762285513</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>53.5921990493777</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>40.89822162015881</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>53.83979569318458</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>40.28329192882606</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>55.36210281376976</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>36.39337880648471</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>56.24482092025164</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>35.64111817548209</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>56.84206106032972</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>36.58230748438632</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>56.90051290909949</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>36.66347251373095</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>57.12778678552138</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>37.22767762923117</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>56.74282897042981</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>37.5031770210522</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -634,94 +747,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>57.94993237714486</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>47.92715333386469</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>59.10177837984119</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>46.40780095062229</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>59.71670807117393</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>46.16020430681542</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>63.60662119351529</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>44.63789718623024</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>64.35888182451792</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>43.75517907974836</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>63.4176925156137</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>43.1579389396703</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>63.33652748626903</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>43.0994870909005</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>62.77232237076885</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>42.87221321447863</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>62.4968229789478</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>43.25717102957019</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -732,94 +883,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>43.23432343234323</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>56.76567656765676</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>42.7546271268082</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>57.24537287319181</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>43.04891915296302</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>56.95108084703697</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>43.47826086956522</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>56.52173913043478</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>45.22111073649057</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>54.77888926350942</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>45.53869247490532</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>54.46130752509469</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>44.91466557718395</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>55.08533442281604</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>45.14759087124535</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>54.85240912875465</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>44.5138511242606</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>55.4861488757394</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -830,94 +1019,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>40.13109326935306</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>53.66244640466659</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>39.91151737826704</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>54.40226312465065</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>40.06840797448502</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>53.97056966855897</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>39.3060487324186</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>52.34952699328817</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>41.09396353035901</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>50.65174205737786</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>42.19455660734609</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>51.11717165753547</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>41.64757144819974</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>51.81824029383183</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>42.28284814265938</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>51.98766640016868</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>41.60113177843973</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>52.57342952991853</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -928,94 +1155,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Flávio</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>46.3375535953334</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>59.86890673064693</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>45.59773687534936</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>60.08848262173297</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>46.02943033144103</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>59.93159202551497</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>47.65047300671183</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>60.6939512675814</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>49.34825794262213</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>58.90603646964098</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>48.88282834246454</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>57.80544339265391</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>48.18175970616815</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>58.35242855180024</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>48.01233359983132</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>57.71715185734062</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>47.42657047008147</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>58.39886822156027</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1026,33 +1291,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>observacoes_publicadas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>primeira_data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>ultima_data</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>numero_institutos</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>institutos</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>amostras_segmento_publicadas</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>fallbacks_amostra_segmento</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1355,25 @@
       <c r="B2" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="7" t="n">
         <v>46109</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Futura, Ideia, Nexus, Paraná Pesquisas</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1086,19 +1385,29 @@
       <c r="B3" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="7" t="n">
         <v>46109</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="7" t="n">
         <v>46215</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Futura, Ideia, Nexus, Paraná Pesquisas</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1109,16 +1418,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -1130,9 +1443,9 @@
           <t>Universo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Brasil, 2º turno, estimulada, Lula × Flávio.</t>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Brasil, 2º turno, estimulada, Lula × Flávio Bolsonaro.</t>
         </is>
       </c>
     </row>
@@ -1142,9 +1455,9 @@
           <t>Abertura</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Grupos publicados de sexo; rótulos equivalentes são harmonizados conforme a aba Metodologia.</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Grupos publicados de sexo; somente rótulos equivalentes são harmonizados.</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1467,7 @@
           <t>Medida</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Lula e adversário convertidos para votos válidos dentro de cada grupo.</t>
         </is>
@@ -1163,28 +1476,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amostra e IC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Usa amostra do segmento quando publicada; na ausência, o código aplica fallback conservador e isso não equivale à margem de erro total da pesquisa.</t>
+          <t>Cobertura mínima</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Exige ao menos dois grupos e duas datas publicadas em cada grupo desenhado.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Amostra e faixa</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Usa amostra do segmento quando publicada; na ausência, aplica fallback conservador. A faixa é apenas amostral e aproximada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Interpretação</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral.</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral nem probabilidade de vitória.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1195,128 +1521,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>instituto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>tipo_pesquisa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>frequencia_original</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>amostra_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>margem_erro_pp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>nivel_confianca_pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>turno</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>tipo_cenario</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>cenario</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>adversario</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>nivel_geografico</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>geografia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>segmento_tipo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>amostra_segmento</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>lula_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>adversario_pct</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>outros_candidatos_pct</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>brancos_nulos_indecisos_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>base_voto</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>_linha_excel</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>peso_legacy</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>grupo_abertura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="7" t="n">
         <v>46109</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1337,7 +1694,7 @@
       <c r="E2" t="n">
         <v>2080</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G2" t="n">
@@ -1386,16 +1743,16 @@
       <c r="P2" t="n">
         <v>979</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>39.3</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="6" t="n">
         <v>51.6</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="6" t="n">
         <v>9.1</v>
       </c>
       <c r="U2" t="inlineStr">
@@ -1404,16 +1761,19 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>432</v>
+      </c>
+      <c r="W2" s="6" t="n">
         <v>0.8208955223880596</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="7" t="n">
         <v>46109</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1434,7 +1794,7 @@
       <c r="E3" t="n">
         <v>2080</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G3" t="n">
@@ -1483,16 +1843,16 @@
       <c r="P3" t="n">
         <v>1101</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="6" t="n">
         <v>48.3</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="6" t="n">
         <v>39.5</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="6" t="n">
         <v>12.2</v>
       </c>
       <c r="U3" t="inlineStr">
@@ -1501,16 +1861,19 @@
         </is>
       </c>
       <c r="V3" t="n">
+        <v>431</v>
+      </c>
+      <c r="W3" s="6" t="n">
         <v>0.8208955223880596</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="7" t="n">
         <v>46110</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1595,16 +1958,19 @@
         </is>
       </c>
       <c r="V4" t="n">
+        <v>569</v>
+      </c>
+      <c r="W4" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="7" t="n">
         <v>46110</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1689,16 +2055,19 @@
         </is>
       </c>
       <c r="V5" t="n">
+        <v>568</v>
+      </c>
+      <c r="W5" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1783,16 +2152,19 @@
         </is>
       </c>
       <c r="V6" t="n">
+        <v>841</v>
+      </c>
+      <c r="W6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="7" t="n">
         <v>46138</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1877,16 +2249,19 @@
         </is>
       </c>
       <c r="V7" t="n">
+        <v>840</v>
+      </c>
+      <c r="W7" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="7" t="n">
         <v>46166</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1971,16 +2346,19 @@
         </is>
       </c>
       <c r="V8" t="n">
+        <v>1089</v>
+      </c>
+      <c r="W8" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="7" t="n">
         <v>46166</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -2065,16 +2443,19 @@
         </is>
       </c>
       <c r="V9" t="n">
+        <v>1088</v>
+      </c>
+      <c r="W9" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -2095,7 +2476,7 @@
       <c r="E10" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G10" t="n">
@@ -2141,16 +2522,16 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="6" t="n">
         <v>42.2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="6" t="n">
         <v>49.1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="U10" t="inlineStr">
@@ -2159,16 +2540,19 @@
         </is>
       </c>
       <c r="V10" t="n">
+        <v>1284</v>
+      </c>
+      <c r="W10" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="7" t="n">
         <v>46185</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2189,7 +2573,7 @@
       <c r="E11" t="n">
         <v>2000</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G11" t="n">
@@ -2235,16 +2619,16 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="6" t="n">
         <v>54.5</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="6" t="n">
         <v>36.2</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="6" t="n">
         <v>9.4</v>
       </c>
       <c r="U11" t="inlineStr">
@@ -2253,16 +2637,19 @@
         </is>
       </c>
       <c r="V11" t="n">
+        <v>1283</v>
+      </c>
+      <c r="W11" s="6" t="n">
         <v>0.9194029850746268</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2347,16 +2734,19 @@
         </is>
       </c>
       <c r="V12" t="n">
+        <v>1486</v>
+      </c>
+      <c r="W12" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="7" t="n">
         <v>46187</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2441,16 +2831,19 @@
         </is>
       </c>
       <c r="V13" t="n">
+        <v>1485</v>
+      </c>
+      <c r="W13" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2535,16 +2928,19 @@
         </is>
       </c>
       <c r="V14" t="n">
+        <v>1721</v>
+      </c>
+      <c r="W14" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="7" t="n">
         <v>46201</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2629,16 +3025,19 @@
         </is>
       </c>
       <c r="V15" t="n">
+        <v>1720</v>
+      </c>
+      <c r="W15" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2659,7 +3058,7 @@
       <c r="E16" t="n">
         <v>1500</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="G16" t="n">
@@ -2705,16 +3104,16 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="6" t="n">
         <v>39.2</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16" s="6" t="n">
         <v>46.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" s="6" t="n">
         <v>14.6</v>
       </c>
       <c r="U16" t="inlineStr">
@@ -2723,16 +3122,19 @@
         </is>
       </c>
       <c r="V16" t="n">
+        <v>1893</v>
+      </c>
+      <c r="W16" s="6" t="n">
         <v>0.7432835820895523</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="7" t="n">
         <v>46209</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2753,7 +3155,7 @@
       <c r="E17" t="n">
         <v>1500</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="G17" t="n">
@@ -2799,16 +3201,16 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="6" t="n">
         <v>50.4</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" s="6" t="n">
         <v>34.2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" s="6" t="n">
         <v>15.3</v>
       </c>
       <c r="U17" t="inlineStr">
@@ -2817,16 +3219,19 @@
         </is>
       </c>
       <c r="V17" t="n">
+        <v>1892</v>
+      </c>
+      <c r="W17" s="6" t="n">
         <v>0.7432835820895523</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2911,16 +3316,19 @@
         </is>
       </c>
       <c r="V18" t="n">
+        <v>1965</v>
+      </c>
+      <c r="W18" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="7" t="n">
         <v>46215</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -3005,15 +3413,19 @@
         </is>
       </c>
       <c r="V19" t="n">
+        <v>1964</v>
+      </c>
+      <c r="W19" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>